--- a/output/xlsform_hab9.xlsx
+++ b/output/xlsform_hab9.xlsx
@@ -36227,7 +36227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36544,12 +36544,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>afw</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>afw.</t>
         </is>
       </c>
     </row>
@@ -36561,12 +36561,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>zs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>zs (&lt;3 ex.)</t>
         </is>
       </c>
     </row>
@@ -36578,12 +36578,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>s</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>s (4-10 ex.)</t>
         </is>
       </c>
     </row>
@@ -36595,12 +36595,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>wt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>wt (10-50 ex.)</t>
         </is>
       </c>
     </row>
@@ -36612,12 +36612,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5_10perc</t>
+          <t>t</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5-10%</t>
+          <t>t (&gt;50 ex.)</t>
         </is>
       </c>
     </row>
@@ -36629,12 +36629,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10_20perc</t>
+          <t>5_10perc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10-20%</t>
+          <t>5-10</t>
         </is>
       </c>
     </row>
@@ -36646,12 +36646,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20_30perc</t>
+          <t>10_20perc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20-30%</t>
+          <t>10-20</t>
         </is>
       </c>
     </row>
@@ -36663,12 +36663,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30_40perc</t>
+          <t>20_30perc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>30-40%</t>
+          <t>20-30</t>
         </is>
       </c>
     </row>
@@ -36680,12 +36680,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>40_50perc</t>
+          <t>30_40perc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>40-50%</t>
+          <t>30-40</t>
         </is>
       </c>
     </row>
@@ -36697,12 +36697,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>50_60perc</t>
+          <t>40_50perc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>50-60%</t>
+          <t>40-50</t>
         </is>
       </c>
     </row>
@@ -36714,12 +36714,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>60_70perc</t>
+          <t>50_60perc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>60-70%</t>
+          <t>50-60</t>
         </is>
       </c>
     </row>
@@ -36731,12 +36731,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>70_80perc</t>
+          <t>60_70perc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>70-80%</t>
+          <t>60-70</t>
         </is>
       </c>
     </row>
@@ -36748,12 +36748,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>80_90perc</t>
+          <t>70_80perc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>80-90%</t>
+          <t>70-80</t>
         </is>
       </c>
     </row>
@@ -36765,12 +36765,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90_95perc</t>
+          <t>80_90perc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-90</t>
         </is>
       </c>
     </row>
@@ -36782,29 +36782,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>95_100perc</t>
+          <t>90_95perc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>lijst_subhabitats</t>
+          <t>LSVI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>95_100perc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>95-100</t>
         </is>
       </c>
     </row>
@@ -36816,12 +36816,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9110</t>
         </is>
       </c>
     </row>
@@ -36833,12 +36833,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>9120</t>
         </is>
       </c>
     </row>
@@ -36850,12 +36850,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>9130</t>
         </is>
       </c>
     </row>
@@ -36867,12 +36867,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>9150</t>
         </is>
       </c>
     </row>
@@ -36884,12 +36884,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9160</t>
         </is>
       </c>
     </row>
@@ -36901,12 +36901,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>91e0_vm</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>91E0_VM</t>
+          <t>9190</t>
         </is>
       </c>
     </row>
@@ -36918,12 +36918,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>91e0_vo</t>
+          <t>91e0_vm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>91E0_VO</t>
+          <t>91E0_VM</t>
         </is>
       </c>
     </row>
@@ -36935,12 +36935,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>91e0_vc</t>
+          <t>91e0_vo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>91E0_VC</t>
+          <t>91E0_VO</t>
         </is>
       </c>
     </row>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>91e0_vn</t>
+          <t>91e0_vc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>91E0_VN</t>
+          <t>91E0_VC</t>
         </is>
       </c>
     </row>
@@ -36969,12 +36969,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>91e0_va</t>
+          <t>91e0_vn</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>91E0_VA</t>
+          <t>91E0_VN</t>
         </is>
       </c>
     </row>
@@ -36986,12 +36986,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>91e0_sf</t>
+          <t>91e0_va</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>91E0_SF</t>
+          <t>91E0_VA</t>
         </is>
       </c>
     </row>
@@ -37003,10 +37003,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>91e0_sf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>91E0_SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>lijst_subhabitats</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>91f0</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>91F0</t>
         </is>
